--- a/data-manipulation-scripts/sheets-cleanup/sheets/SENSOR ABS.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/SENSOR ABS.xlsx
@@ -28,13 +28,13 @@
     <t>070341176924</t>
   </si>
   <si>
-    <t>SENSOR ABS DIANT YS250 FAZER 2018 A 2023 350493</t>
+    <t>SENSOR ABS DIANTEIRO IRON YS250 FAZER 2018 A 2023 350493</t>
   </si>
   <si>
     <t>070341176917</t>
   </si>
   <si>
-    <t>SENSOR ABS TRAS IRON YS250 FAZER2018 A 2023 350494</t>
+    <t>SENSOR ABS TRASEIRO IRON YS250 FAZER 2018 A 2023 350494</t>
   </si>
 </sst>
 </file>
@@ -92,10 +92,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -359,10 +359,12 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>2.0</v>
       </c>
-      <c r="D2" s="5"/>
+      <c r="D2" s="4">
+        <v>115.0</v>
+      </c>
       <c r="E2" s="6"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
@@ -393,10 +395,12 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>2.0</v>
       </c>
-      <c r="D3" s="5"/>
+      <c r="D3" s="4">
+        <v>115.0</v>
+      </c>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
